--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-systemische-therapie-intention.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-systemische-therapie-intention.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T22:11:44+00:00</t>
+    <t>2026-08-22T22:31:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
